--- a/ig/DM_FINESS_New/ValueSet-1.2.250.1.213.1.1.5.732.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-1.2.250.1.213.1.1.5.732.xlsx
@@ -10,14 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -67,13 +65,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-03T01:00:00+02:00</t>
+    <t>2023-08-03T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -94,55 +92,55 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>O72</t>
+  </si>
+  <si>
+    <t>Hémorragie du postpartum</t>
+  </si>
+  <si>
+    <t>O99</t>
+  </si>
+  <si>
+    <t>Autres maladies de la mère classées ailleurs, mais compliquant la grossesse, l'accouchement et la puerpéralité</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-cim-10</t>
+  </si>
+  <si>
+    <t>MED-1247</t>
+  </si>
+  <si>
+    <t>Etat du périnée</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+  </si>
+  <si>
     <t>11884-4</t>
   </si>
   <si>
     <t>Age gestationnel du fœtus (estimation clinique)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.1</t>
-  </si>
-  <si>
-    <t>O72</t>
-  </si>
-  <si>
-    <t>Hémorragie du postpartum</t>
-  </si>
-  <si>
-    <t>O99</t>
-  </si>
-  <si>
-    <t>Autres maladies de la mère classées ailleurs, mais compliquant la grossesse, l'accouchement et la puerpéralité</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.3</t>
-  </si>
-  <si>
     <t>63893-2</t>
   </si>
   <si>
     <t>Issue de la grossesse</t>
   </si>
   <si>
-    <t>MED-1247</t>
-  </si>
-  <si>
-    <t>Etat du périnée</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
-  </si>
-  <si>
     <t>11638-4</t>
   </si>
   <si>
     <t>Nombre d'enfants vivants</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -398,52 +396,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -461,34 +413,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -515,26 +467,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -542,9 +494,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -561,72 +513,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B2" t="s" s="2">
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>41</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
